--- a/Original - QPS TIR and SURV Import 080326.xlsx
+++ b/Original - QPS TIR and SURV Import 080326.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdo365-my.sharepoint.us/personal/larry_jacoinski_gd-ms_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CWH Projects\TIRs\Project_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{07D8A3BC-B531-4A18-AE09-74994A52E86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6940D316-36EC-4DF2-A871-E376F874AA49}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F88A7EB-81F9-4D8C-A1A9-392118151547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12360" xr2:uid="{DC24C4A9-5179-41D9-9172-9A2AE2C1594A}"/>
+    <workbookView xWindow="-23148" yWindow="-1356" windowWidth="23256" windowHeight="13680" xr2:uid="{DC24C4A9-5179-41D9-9172-9A2AE2C1594A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9046,23 +9046,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB83956A-2C0B-41D4-8FBB-28FC2B2498F7}">
   <dimension ref="A1:AX812"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="33.5703125" customWidth="1"/>
-    <col min="9" max="10" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.42578125" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" customWidth="1"/>
-    <col min="14" max="14" width="70.5703125" customWidth="1"/>
-    <col min="15" max="15" width="31.140625" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" style="2"/>
-    <col min="18" max="26" width="20" customWidth="1"/>
-    <col min="27" max="31" width="8.85546875" customWidth="1"/>
-    <col min="32" max="32" width="25.42578125" customWidth="1"/>
-    <col min="33" max="33" width="8.85546875" customWidth="1"/>
-    <col min="34" max="34" width="17.85546875" customWidth="1"/>
-    <col min="35" max="35" width="16.42578125" customWidth="1"/>
-    <col min="36" max="36" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="30" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="21" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="3" customFormat="1" x14ac:dyDescent="0.25">
